--- a/docs/samples/领料单-样例.xlsx
+++ b/docs/samples/领料单-样例.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="46">
   <si>
     <t>【领料单】</t>
   </si>
@@ -50,9 +50,6 @@
   </si>
   <si>
     <t>领料工序：</t>
-  </si>
-  <si>
-    <t>裁剪</t>
   </si>
   <si>
     <t>领料单位：</t>
@@ -657,67 +654,67 @@
         <v>12</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>15</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="J6" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -725,19 +722,19 @@
         <v>1</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>36</v>
       </c>
       <c r="G7" s="7">
         <v>2500</v>
@@ -757,19 +754,19 @@
         <v>2</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="F8" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>41</v>
       </c>
       <c r="G8" s="7">
         <v>500</v>
@@ -789,10 +786,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>43</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>6</v>
@@ -801,7 +798,7 @@
         <v>6</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="7">
@@ -814,7 +811,7 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -836,7 +833,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
